--- a/artfynd/A 63327-2025 artfynd.xlsx
+++ b/artfynd/A 63327-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130981914</v>
+        <v>130981911</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>91830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,31 +985,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1012,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437688</v>
+        <v>437697</v>
       </c>
       <c r="R5" t="n">
-        <v>6792409</v>
+        <v>6792416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1056,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1072,17 +1068,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130981911</v>
+        <v>130981914</v>
       </c>
       <c r="B6" t="n">
-        <v>91830</v>
+        <v>57881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,26 +1086,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1117,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437697</v>
+        <v>437688</v>
       </c>
       <c r="R6" t="n">
-        <v>6792416</v>
+        <v>6792409</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,7 +1162,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 63327-2025 artfynd.xlsx
+++ b/artfynd/A 63327-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130981911</v>
+        <v>130981914</v>
       </c>
       <c r="B5" t="n">
-        <v>91830</v>
+        <v>57881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,26 +985,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1012,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437697</v>
+        <v>437688</v>
       </c>
       <c r="R5" t="n">
-        <v>6792416</v>
+        <v>6792409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1061,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1068,17 +1072,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130981914</v>
+        <v>130981911</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>91830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,31 +1090,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1118,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437688</v>
+        <v>437697</v>
       </c>
       <c r="R6" t="n">
-        <v>6792409</v>
+        <v>6792416</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1161,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 63327-2025 artfynd.xlsx
+++ b/artfynd/A 63327-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130981927</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130981931</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130981914</v>
+        <v>130981911</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>91831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,31 +985,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1012,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437688</v>
+        <v>437697</v>
       </c>
       <c r="R5" t="n">
-        <v>6792409</v>
+        <v>6792416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1056,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1072,17 +1068,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130981911</v>
+        <v>130981914</v>
       </c>
       <c r="B6" t="n">
-        <v>91830</v>
+        <v>57881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,26 +1086,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1117,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437697</v>
+        <v>437688</v>
       </c>
       <c r="R6" t="n">
-        <v>6792416</v>
+        <v>6792409</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,7 +1162,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
         <v>130981936</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130981937</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>130981926</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>130981933</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>130981930</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>130981935</v>
       </c>
       <c r="B12" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>130981929</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>130981928</v>
       </c>
       <c r="B16" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>130981938</v>
       </c>
       <c r="B17" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 63327-2025 artfynd.xlsx
+++ b/artfynd/A 63327-2025 artfynd.xlsx
@@ -977,7 +977,7 @@
         <v>130981911</v>
       </c>
       <c r="B5" t="n">
-        <v>91831</v>
+        <v>91834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63327-2025 artfynd.xlsx
+++ b/artfynd/A 63327-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130981927</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130981931</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>130981911</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130981936</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130981937</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>130981926</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130981933</v>
+        <v>130981930</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437877</v>
+        <v>437745</v>
       </c>
       <c r="R10" t="n">
-        <v>6792522</v>
+        <v>6792623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130981930</v>
+        <v>130981933</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437745</v>
+        <v>437877</v>
       </c>
       <c r="R11" t="n">
-        <v>6792623</v>
+        <v>6792522</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,45 +1665,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130981935</v>
+        <v>130981909</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>57073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brottvasslen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437656</v>
+        <v>437657</v>
       </c>
       <c r="R12" t="n">
-        <v>6792404</v>
+        <v>6792398</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,60 +1763,52 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Alfhild Sehlin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130981909</v>
+        <v>130981935</v>
       </c>
       <c r="B13" t="n">
-        <v>57073</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brottvasslen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437657</v>
+        <v>437656</v>
       </c>
       <c r="R13" t="n">
-        <v>6792398</v>
+        <v>6792404</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Alfhild Sehlin</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
         <v>130981929</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>130981928</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>130981938</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 63327-2025 artfynd.xlsx
+++ b/artfynd/A 63327-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981911</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981926</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981927</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981928</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981929</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981930</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981931</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981932</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981933</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981934</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981935</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981936</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981937</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981938</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981906</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2236,6 +2316,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981913</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981914</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2446,6 +2536,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981915</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2551,6 +2646,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981916</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2656,6 +2756,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981909</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2763,6 +2868,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981919</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2860,8 +2970,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130981918</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>